--- a/AAII_Financials/Quarterly/SENEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SENEA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>SENEA</t>
   </si>
@@ -656,417 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>444500</v>
+      </c>
+      <c r="E8" s="3">
         <v>407500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>298700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>331100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>473300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>439800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>265200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>332400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>445600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>372300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>235000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>304800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>484400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>390300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>288200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>307900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>393000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>370000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>264900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>262600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>372200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>320700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>244100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>299700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>354900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>568800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>241200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>280700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>356800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>352600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>390400</v>
+      </c>
+      <c r="E9" s="3">
         <v>349400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>243400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>345200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>419500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>398100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>242400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>312100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>329500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>201400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>247800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>406700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>341400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>239600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>261500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>340700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>345900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>245800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>248800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>374300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>309700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>227300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>288500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>326100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>533700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>227700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>259600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>318800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>321600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E10" s="3">
         <v>58100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-14100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>53800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>45000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>57000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>77700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>48900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>52300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-2100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>28800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>35100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>38000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1292,73 +1311,73 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-35800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>300</v>
       </c>
       <c r="R14" s="3">
         <v>300</v>
       </c>
       <c r="S14" s="3">
+        <v>300</v>
+      </c>
+      <c r="T14" s="3">
         <v>800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>800</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>9900</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>100</v>
       </c>
       <c r="AB14" s="3">
         <v>100</v>
@@ -1367,16 +1386,19 @@
         <v>100</v>
       </c>
       <c r="AD14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>413700</v>
+      </c>
+      <c r="E17" s="3">
         <v>369100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>263200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>368000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>443400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>418000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>258600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>331600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>421900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>350400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>217300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>272300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>393800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>362600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>257900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>280800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>359900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>362600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>262000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>272200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>395900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>325500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>244100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>314400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>345400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>565900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>241900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>275900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>342400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>340600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E18" s="3">
         <v>38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-36900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>90600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-23700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,192 +1748,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-700</v>
       </c>
       <c r="S20" s="3">
         <v>-700</v>
       </c>
       <c r="T20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E21" s="3">
         <v>43700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-30900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>27300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>34900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>34700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>15700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1929,8 +1968,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
@@ -1947,8 +1986,8 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>300</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>300</v>
@@ -1957,14 +1996,14 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
+        <v>300</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -1992,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E23" s="3">
         <v>32600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>90000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>23700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
         <v>7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>17500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E26" s="3">
         <v>24800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>24700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-20000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2573,17 +2633,17 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2591,15 +2651,15 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2607,28 +2667,28 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>34100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>14800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2636,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E32" s="3">
         <v>5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>700</v>
       </c>
       <c r="S32" s="3">
         <v>700</v>
       </c>
       <c r="T32" s="3">
+        <v>700</v>
+      </c>
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>24700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>25300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>24700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>25300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E41" s="3">
         <v>12100</v>
-      </c>
-      <c r="E41" s="3">
-        <v>12300</v>
       </c>
       <c r="F41" s="3">
         <v>12300</v>
       </c>
       <c r="G41" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H41" s="3">
         <v>12500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11300</v>
-      </c>
-      <c r="M41" s="3">
-        <v>59800</v>
       </c>
       <c r="N41" s="3">
         <v>59800</v>
       </c>
       <c r="O41" s="3">
+        <v>59800</v>
+      </c>
+      <c r="P41" s="3">
         <v>14100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
-      </c>
-      <c r="W41" s="3">
-        <v>12800</v>
       </c>
       <c r="X41" s="3">
         <v>12800</v>
       </c>
       <c r="Y41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,376 +3626,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E43" s="3">
         <v>129300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>85000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>104100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>94900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>162500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>90900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>125600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>151600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>72100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>101500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>96600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>134800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>68900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>121800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>86700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>123400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>79600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>84300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>101300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>90100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>67400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>68500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>97800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>79700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>146600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>67400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>102700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>968900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1013400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>735100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>670900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>780500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>821300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>517100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>404000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>482000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>608200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>414700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>343100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>410900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>550700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>423800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>411600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>493100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>575200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>493500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>501700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>575900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>683900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>569300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>547000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>770700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>656300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>633500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>628900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>699400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>801700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>36900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>52300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>111700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>167500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>16200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1078300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1157500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>837900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>794000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>893800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1004900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>629100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>550700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>605200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>783300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>559900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>516300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>535800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>714500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>523900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>551600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>600000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>723900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>593700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>603200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>710000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>850200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>679300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>741100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>855100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>936500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>731900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>719100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>793200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>934700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,100 +4101,106 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>351400</v>
+      </c>
+      <c r="E48" s="3">
         <v>354600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>358500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>358000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>357600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>345000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>344500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>336900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>332600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>340300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>335800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>321400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>304000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>323900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>329100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>322800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>322000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>314600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>324200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>239300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>246000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>242400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>272000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>258500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>272400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>253700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>269800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>237500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>218000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>207500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4181,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E52" s="3">
         <v>59600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>60700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>53500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>53000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>53900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>54700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>64600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>64900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>72600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>71700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>34900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>29200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>23700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>21600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>42500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1489500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1571700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1256600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1212700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1304800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1402900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1027500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>942300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1002400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1188400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>968300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>909300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>858500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1066800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>883000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>909300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>932700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1045700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>925300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>848900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>962100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1121900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>964200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1028800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1134200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1213900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1006900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>978300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1053700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1185200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E57" s="3">
         <v>321600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>117700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>156100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>345200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>142200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>87600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>111300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>268900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>125600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>74100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>230100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>99600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>71200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>84300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>195700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>77600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>61000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>93600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>212100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>98500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>56800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>102000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>224100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>109800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>72800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>98200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E58" s="3">
         <v>31600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>50000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>69600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>28300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>320600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E59" s="3">
         <v>79700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>69500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>64400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>78100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>71500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>50200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>82100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>84800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>67600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>54600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>76700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>63000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>74400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>130300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>95900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>45700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>96400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>128200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>112600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E60" s="3">
         <v>432800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>200200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>156200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>246900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>445400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>216000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>173200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>199900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>372200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>201700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>158100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>188100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>380600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>177800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>149700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>173000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>286600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>151900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>112400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>468800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>295500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>180300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>138600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>242000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>327200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>164200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>177800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>238800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>359600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>624500</v>
+      </c>
+      <c r="E61" s="3">
         <v>506900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>430400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>450000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>417300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>334800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>185500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>129600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>145400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>166300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>116100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>113300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>114600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>131000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>167100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>241400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>252300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>270800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>276600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>297200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>40400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>384300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>351700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>442100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>449200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>424100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>384300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>363300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>369600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>373300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E62" s="3">
         <v>48800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>50200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>51800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>54500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>60500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>60100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>123200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>123000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>123800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>72100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>75600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>83100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>32800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>32300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>29800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>33100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>38700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>896100</v>
+      </c>
+      <c r="E66" s="3">
         <v>988500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>680800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>658000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>719800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>834700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>459200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>363200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>407800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>602100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>380900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>331500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>355000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>634800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>467900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>514900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>497500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>633000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>511500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>431400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>542000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>712100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>561900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>617800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>711800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>784400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>573400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>553100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>647100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>785600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5862,7 +6029,7 @@
         <v>400</v>
       </c>
       <c r="G70" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H70" s="3">
         <v>600</v>
@@ -5877,7 +6044,7 @@
         <v>600</v>
       </c>
       <c r="L70" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M70" s="3">
         <v>700</v>
@@ -5931,7 +6098,7 @@
         <v>700</v>
       </c>
       <c r="AD70" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="AE70" s="3">
         <v>1300</v>
@@ -5939,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>706800</v>
+      </c>
+      <c r="E72" s="3">
         <v>689100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>664400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>641300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>679100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>658100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>637100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>632100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>630300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>611700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>600000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>585900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>571000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>498600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>480500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>459800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>438600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>413200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>408600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>409500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>418100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>404100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>395000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>403800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>401500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>407900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>409300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>401100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>400800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>593100</v>
+      </c>
+      <c r="E76" s="3">
         <v>582900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>575500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>554400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>584500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>567600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>567700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>578400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>593900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>585700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>586700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>577200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>502900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>431400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>414400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>393700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>434500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>412000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>413100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>416800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>419300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>409100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>401600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>410400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>421700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>428800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>432800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>423900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>405300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>398300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>24700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>25300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E83" s="3">
         <v>11100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>8000</v>
       </c>
       <c r="Y83" s="3">
         <v>8000</v>
       </c>
       <c r="Z83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>8400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>7700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-101800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-51300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-55900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-110800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-71600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>80100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>50700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>50700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>87000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>20400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>34000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>18700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-48200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22700</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-11800</v>
       </c>
       <c r="M94" s="3">
         <v>-11800</v>
       </c>
       <c r="N94" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="O94" s="3">
         <v>-30400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>58900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>12500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>54800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,100 +8496,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E100" s="3">
         <v>58300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>77200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>126000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-31100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-75700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-81100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-35000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-32400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-20000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-64500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-34400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>20600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-89400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>14500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>47100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8438,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48600</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>45700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1300</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SENEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SENEA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SENEA</t>
   </si>
@@ -656,429 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>304700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>308000</v>
+      </c>
+      <c r="F8" s="3">
         <v>444500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>407500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>298700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>331100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>473300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>439800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>265200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>332400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>445600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>372300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>235000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>304800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>484400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>390300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>288200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>307900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>393000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>370000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>264900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>262600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>372200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>320700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>244100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>299700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>354900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>568800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>241200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>280700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>356800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>352600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>287200</v>
+      </c>
+      <c r="F9" s="3">
         <v>390400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>349400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>243400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>345200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>419500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>398100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>242400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>312100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>400600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>329500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>201400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>247800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>406700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>341400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>239600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>261500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>340700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>345900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>245800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>248800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>374300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>309700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>227300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>288500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>326100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>533700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>227700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>259600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>318800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>321600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F10" s="3">
         <v>54100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>58100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>55300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-14100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>53800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>41700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>22900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>20300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>45000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>42800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>33600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>57000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>77700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>48900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>48600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>46400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>52300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>24100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>19100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>13800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>11000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>16800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>11200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>28800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>35100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>13500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>21100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>38000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1138,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1235,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,103 +1336,115 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-35800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>4800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>9400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>800</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>9900</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>100</v>
       </c>
       <c r="AD14" s="3">
         <v>100</v>
       </c>
       <c r="AE14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>1300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1538,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1576,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>279300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>305400</v>
+      </c>
+      <c r="F17" s="3">
         <v>413700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>369100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>263200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>368000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>443400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>418000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>258600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>331600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>421900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>350400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>217300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>272300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>393800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>362600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>257900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>280800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>359900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>362600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>262000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>272200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>395900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>325500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>244100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>314400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>345400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>565900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>241900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>275900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>342400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>340600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F18" s="3">
         <v>30800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>35500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-36900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>29900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>21800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>21900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>17700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>32500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>90600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>27700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>30300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>27100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>33100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-9600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-23700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>9500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>14400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,198 +1815,212 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-6600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-13300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F21" s="3">
         <v>39500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>43700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>40900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-30900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>38100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>31000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>16500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>11100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>33700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>24300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>27200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>27300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>98200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>31900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>34900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>34700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>40300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>13700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>9100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-4100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>5200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>15400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>15700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>5800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>8500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>18500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>15700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1971,11 +2051,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
@@ -1989,27 +2069,27 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>300</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>300</v>
       </c>
       <c r="V22" s="3">
+        <v>300</v>
+      </c>
+      <c r="W22" s="3">
+        <v>300</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -2034,198 +2114,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F23" s="3">
         <v>23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>32600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>30300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-41500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>27600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>21000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>24400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>15200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>18600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>19300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>90000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>23700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>27000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>26100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>32100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-11800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-26900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>7600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>12300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-8400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>4900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>3600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>17500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>5600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>6300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>5100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>4500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2417,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>17700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>24800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>23100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-33100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>21100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>16100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>18700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>11700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>14800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>72500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>20700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>21000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>24400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-8600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>8900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>7800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F27" s="3">
         <v>17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>24700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>23100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-32900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>21000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>16100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>18600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>11600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>14100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>14800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>72200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>20600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>20900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>24300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-8600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-15600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>8800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>7700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2720,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,71 +2758,77 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>1000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>34100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>14800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>1400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2922,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +3023,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F32" s="3">
         <v>7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>6600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>13300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>3200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>4400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>2600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>2100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F33" s="3">
         <v>17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>24700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>23100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-32900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>21000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>16100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>18600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>14100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>14800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>72200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>20600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>21100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>25300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-8600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>14100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>9100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>7700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>7700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3326,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F35" s="3">
         <v>17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>24700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>23100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-32900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>21000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>16100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>18600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>14100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>14800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>72200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>20600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>21100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>25300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-8600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>14100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>9100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>7700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>7700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3574,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3611,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>59800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>59800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>14100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>13900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>17600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>16900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>11500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>12800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>12800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>15100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>14900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>15800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>12000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>10300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,388 +3809,418 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>79800</v>
+      </c>
+      <c r="F43" s="3">
         <v>91100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>129300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>85000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>104100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>94900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>162500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>90900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>125600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>95300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>151600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>72100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>101500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>96600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>134800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>68900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>121800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>86700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>123400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>79600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>85300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>84300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>101300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>90100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>67400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>68500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>97800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>79700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>146600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>67400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>102700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>841800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>872700</v>
+      </c>
+      <c r="F44" s="3">
         <v>968900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1013400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>735100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>670900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>780500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>821300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>517100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>404000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>482000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>608200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>414700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>343100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>410900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>550700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>423800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>411600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>493100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>575200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>493500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>501700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>575900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>683900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>569300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>547000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>770700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>656300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>633500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>628900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>699400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>801700</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F45" s="3">
         <v>11200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>16900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>12300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>13300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>14100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>19500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>7700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>4700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>36900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>52300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>7200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>111700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>167500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>3700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>16200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>955700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>967000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1078300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1157500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>837900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>794000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>893800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1004900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>629100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>550700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>605200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>783300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>559900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>516300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>535800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>714500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>523900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>551600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>600000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>723900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>593700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>603200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>710000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>850200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>679300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>741100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>855100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>936500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>731900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>719100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>793200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>934700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,103 +4314,115 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>345100</v>
+      </c>
+      <c r="F48" s="3">
         <v>351400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>354600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>358500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>358000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>357600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>345000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>344500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>336900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>332600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>340300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>335800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>321400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>304000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>323900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>329100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>322800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>322000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>314600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>324200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>239300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>246000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>242400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>272000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>258500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>272400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>253700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>269800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>237500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>218000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>207500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4516,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4617,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4718,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>71900</v>
+      </c>
+      <c r="F52" s="3">
         <v>59800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>59600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>60200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>60700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>53500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>53000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>53900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>54700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>64600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>64900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>72600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>71700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>18700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>28400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>30000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>34900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>10700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>6400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>29300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>12900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>29200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>23700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>5300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>21600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>42500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4920,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1369100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1489500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1571700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1256600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1212700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1304800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1402900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1027500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>942300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1002400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1188400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>968300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>909300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>858500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1066800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>883000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>909300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>932700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1045700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>925300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>848900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>962100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1121900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>964200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1028800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1134200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1213900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1006900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>978300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1053700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1185200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5062,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +5099,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>40300</v>
+      </c>
+      <c r="F57" s="3">
         <v>125200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>321600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>117700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>69200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>156100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>345200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>142200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>87600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>111300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>268900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>125600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>74100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>98800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>230100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>99600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>71200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>84300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>195700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>77600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>61000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>93600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>212100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>98500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>56800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>102000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>224100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>109800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>72800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>98200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>121400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F58" s="3">
         <v>30600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>31600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>32600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>51600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>21300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>22100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>50000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>35000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>12400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>12300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>11700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>28300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>11100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>69600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>28300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>6600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>6100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>6800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>320600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>18800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>7500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>9700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>7200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>8700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>8500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>12400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>71700</v>
+      </c>
+      <c r="F59" s="3">
         <v>68300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>79700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>49900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>61200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>69500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>78200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>48700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>59500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>76200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>91000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>64400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>55700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>78100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>80900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>71500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>50200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>82100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>84800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>67600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>44600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>54600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>76700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>63000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>74400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>130300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>95900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>45700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>96400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>128200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>112600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>249500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>151000</v>
+      </c>
+      <c r="F60" s="3">
         <v>224000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>432800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>200200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>156200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>246900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>445400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>216000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>173200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>199900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>372200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>201700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>158100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>188100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>380600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>177800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>149700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>173000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>286600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>151900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>112400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>468800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>295500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>180300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>138600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>242000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>327200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>164200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>177800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>238800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>359600</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>484300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>598000</v>
+      </c>
+      <c r="F61" s="3">
         <v>624500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>506900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>430400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>450000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>417300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>334800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>185500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>129600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>145400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>166300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>116100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>113300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>114600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>131000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>167100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>241400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>252300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>270800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>276600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>297200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>40400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>384300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>351700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>442100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>449200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>424100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>384300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>363300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>369600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>373300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F62" s="3">
         <v>47600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>48800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>50200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>51800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>55500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>54500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>57700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>60500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>62500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>63600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>63100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>60100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>52300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>123200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>123000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>123800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>72100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>75600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>83100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>21800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>32800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>32300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>29800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>37100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>20600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>33100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>25000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>16100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>38700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>52700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5802,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5903,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6004,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>780200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>801100</v>
+      </c>
+      <c r="F66" s="3">
         <v>896100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>988500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>680800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>658000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>719800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>834700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>459200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>363200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>407800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>602100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>380900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>331500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>355000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>634800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>467900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>514900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>497500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>633000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>511500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>431400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>542000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>712100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>561900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>617800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>711800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>784400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>573400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>553100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>647100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>785600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6146,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6243,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6344,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6032,10 +6368,10 @@
         <v>400</v>
       </c>
       <c r="H70" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I70" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J70" s="3">
         <v>600</v>
@@ -6047,10 +6383,10 @@
         <v>600</v>
       </c>
       <c r="M70" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N70" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O70" s="3">
         <v>700</v>
@@ -6101,16 +6437,22 @@
         <v>700</v>
       </c>
       <c r="AE70" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="AF70" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="AG70" s="3">
         <v>1300</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6546,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>717200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>704600</v>
+      </c>
+      <c r="F72" s="3">
         <v>706800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>689100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>664400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>641300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>679100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>658100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>637100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>632100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>630300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>611700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>600000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>585900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>571000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>498600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>480500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>459800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>438600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>413200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>408600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>409500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>418100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>404100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>395000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>403800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>401500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>407900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>409300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>401100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>400800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>393000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6748,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6849,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6950,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>588600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>582500</v>
+      </c>
+      <c r="F76" s="3">
         <v>593100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>582900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>575500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>554400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>584500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>567600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>567700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>578400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>593900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>585700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>586700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>577200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>502900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>431400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>414400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>393700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>434500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>412000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>413100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>416800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>419300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>409100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>401600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>410400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>421700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>428800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>432800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>423900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>405300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>398300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7152,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F81" s="3">
         <v>17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>24700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>23100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-32900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>21000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>16100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>18600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>14100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>14800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>72200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>20600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>21100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>25300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-8600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>14100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>9100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>7700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>7700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7400,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F83" s="3">
         <v>16300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>11100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>10600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>10500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>10100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>9500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>9400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>9100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>8600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>8100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>8300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>8200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>7900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>8300</v>
       </c>
       <c r="T83" s="3">
         <v>7900</v>
       </c>
       <c r="U83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="V83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="W83" s="3">
         <v>7300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>7400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>7700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>7500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>8400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>7800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>15300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>7700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>6600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>6200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7598,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7699,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7800,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7901,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8002,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>45200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-101800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-51300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>25000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-23300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-55900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-110800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-22800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>41200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>38900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-71600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>21600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>80100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>16100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-13300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>100300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>12000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>50700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>26800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>37800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>50700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>87000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>13600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>20400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>34000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>18700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-48200</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +8144,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-11700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-14700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-22600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-14600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-19200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-16900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-13200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-31300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-8100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-19200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-18000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-31200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-6700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-9800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-7300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-17500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-22700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8342,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8443,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-11700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-13400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-21700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-14500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-11800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-11800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-30400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>58900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-18300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-17700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-19500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-3400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>12500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>54800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-26400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-21400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8585,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8682,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8783,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8884,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8985,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="F100" s="3">
         <v>109200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>58300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-13300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>36400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>77200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>126000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>39400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-27800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-31100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>34800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-9800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-75700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>24500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-81100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-35000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-32400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-20000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-64500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-34400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>20600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>14500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>47100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>4700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-23900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,99 +9187,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-48600</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>45700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>3800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-2400</v>
       </c>
     </row>
